--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14298,22 +14298,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,29 +14355,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14436,12 +14436,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,7 +14554,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -14564,12 +14564,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13540,12 +13540,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -14148,12 +14148,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14394,22 +14394,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13754,22 +13754,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -14234,22 +14234,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14362,22 +14362,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14948,12 +14948,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13695,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14180,12 +14180,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13695,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,14 +14003,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -14276,12 +14276,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -14276,12 +14276,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,7 +14970,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -14980,12 +14980,12 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14596,12 +14596,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13658,22 +13658,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,29 +14323,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,7 +14490,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14938,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,7 +13466,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14330,22 +14330,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,29 +14355,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14938,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,14 +13555,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13658,22 +13658,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13914,22 +13914,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,29 +14355,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,14 +13651,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -13668,12 +13668,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -14180,12 +14180,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -14394,22 +14394,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
